--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9FB8FC-A5BE-49FA-A07A-F3BB7F8C4778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A979A8-405A-4BA2-BAE0-3C4BE4145D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_items_v8" sheetId="1" r:id="rId1"/>
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A979A8-405A-4BA2-BAE0-3C4BE4145D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD72B85-959E-4825-8172-C6725F24E72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,9 +86,6 @@
     <t>items_atlas_0</t>
   </si>
   <si>
-    <t>diamond</t>
-  </si>
-  <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,6 +118,34 @@
   </si>
   <si>
     <t>argument</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>items_atlas_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木桩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wooden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deadman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -528,10 +553,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -548,10 +573,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -568,38 +593,44 @@
         <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -612,17 +643,20 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>8000</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -639,10 +673,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -650,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD72B85-959E-4825-8172-C6725F24E72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9CBDC8-3846-44E7-8DBE-907C76371868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_items_v8" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,62 +90,107 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>停止时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止时间（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>argument</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>items_atlas_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木桩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wooden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deadman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>INT_C_S</t>
-  </si>
-  <si>
-    <t>停止时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止时间（毫秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>argument</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>items_atlas_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>木箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>木桩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wooden</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deadman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围减速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速万分比，减速带长度，至多生效怪物上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000,3000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,10,1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,5,1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害值，可使用次数，伤害间隔（毫秒）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -153,7 +198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +233,29 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -231,15 +299,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,141 +615,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="6"/>
+    <col min="6" max="6" width="16.125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
+      <c r="E2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="6">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+      <c r="B8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="F8" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+      <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="F9" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="6">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>6000</v>
+      <c r="E10" s="6">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -668,27 +821,134 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EA5096-82D8-4F44-A4FC-DDA768D37A7F}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="17.25" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9CBDC8-3846-44E7-8DBE-907C76371868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF6D26B-0FB9-4904-BB66-107802A1EEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF6D26B-0FB9-4904-BB66-107802A1EEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520BF01F-1E0B-4A6A-9A3C-B6DFC7028A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,6 +191,14 @@
   </si>
   <si>
     <t>伤害值，可使用次数，伤害间隔（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fire_ball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice_ball</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -783,7 +791,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -803,7 +811,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520BF01F-1E0B-4A6A-9A3C-B6DFC7028A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC2FB33-4A66-4C05-AB8E-5119D17786FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_items_v8" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,6 +199,10 @@
   </si>
   <si>
     <t>ice_ball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speed_bump</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +775,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC2FB33-4A66-4C05-AB8E-5119D17786FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998565D-F76A-4506-A8B5-2EB0ACCFDC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_items_v8" sheetId="1" r:id="rId1"/>
@@ -182,14 +182,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10,10,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,5,1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>伤害值，可使用次数，伤害间隔（毫秒）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -203,6 +195,14 @@
   </si>
   <si>
     <t>speed_bump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,10,1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,5,2100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -775,7 +775,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6">
         <v>2</v>
@@ -795,13 +795,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -815,13 +815,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +879,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_items_v8【迷宫-救援道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998565D-F76A-4506-A8B5-2EB0ACCFDC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D4A7D3-CDA4-4553-A621-208B5F1F5439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_items_v8" sheetId="1" r:id="rId1"/>
@@ -198,11 +198,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10,10,1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,5,2100</t>
+    <t>20,5,2100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,7,1500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +801,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -821,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
